--- a/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3653_MA_H5_handles_S2B.xlsx
+++ b/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3653_MA_H5_handles_S2B.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matt/Documents/Shih_Lab_Postdoc/research_projects/crisscross_code/crisscross_kit/crisscross/dna_source_plates/assembly_plates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3748C594-38C4-5942-BC93-FED3AFD74605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="25600" yWindow="620" windowWidth="25600" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Data" sheetId="1" r:id="rId1"/>
     <sheet name="2D Layout" sheetId="2" r:id="rId2"/>
     <sheet name="2D Label" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="1582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="1582">
   <si>
     <t>well</t>
   </si>
@@ -4767,8 +4773,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4845,13 +4851,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4889,7 +4903,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4923,6 +4937,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4957,9 +4972,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5132,18 +5148,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E385"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" customWidth="1"/>
+    <col min="4" max="4" width="66.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5160,7 +5176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -5174,10 +5190,10 @@
         <v>1157</v>
       </c>
       <c r="E2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5191,10 +5207,10 @@
         <v>1158</v>
       </c>
       <c r="E3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -5208,10 +5224,10 @@
         <v>1159</v>
       </c>
       <c r="E4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5225,10 +5241,10 @@
         <v>1160</v>
       </c>
       <c r="E5">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -5242,10 +5258,10 @@
         <v>1161</v>
       </c>
       <c r="E6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -5259,10 +5275,10 @@
         <v>1162</v>
       </c>
       <c r="E7">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -5276,10 +5292,10 @@
         <v>1163</v>
       </c>
       <c r="E8">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -5293,10 +5309,10 @@
         <v>1164</v>
       </c>
       <c r="E9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -5310,10 +5326,10 @@
         <v>1165</v>
       </c>
       <c r="E10">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5327,10 +5343,10 @@
         <v>1166</v>
       </c>
       <c r="E11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -5344,10 +5360,10 @@
         <v>1167</v>
       </c>
       <c r="E12">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -5361,10 +5377,10 @@
         <v>1168</v>
       </c>
       <c r="E13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5378,10 +5394,10 @@
         <v>1169</v>
       </c>
       <c r="E14">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -5395,10 +5411,10 @@
         <v>1170</v>
       </c>
       <c r="E15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -5412,10 +5428,10 @@
         <v>1171</v>
       </c>
       <c r="E16">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -5429,10 +5445,10 @@
         <v>1172</v>
       </c>
       <c r="E17">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -5446,10 +5462,10 @@
         <v>1173</v>
       </c>
       <c r="E18">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -5463,10 +5479,10 @@
         <v>1174</v>
       </c>
       <c r="E19">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -5480,10 +5496,10 @@
         <v>1175</v>
       </c>
       <c r="E20">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -5497,10 +5513,10 @@
         <v>1176</v>
       </c>
       <c r="E21">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -5514,10 +5530,10 @@
         <v>1177</v>
       </c>
       <c r="E22">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -5531,10 +5547,10 @@
         <v>1178</v>
       </c>
       <c r="E23">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -5548,10 +5564,10 @@
         <v>1179</v>
       </c>
       <c r="E24">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -5565,10 +5581,10 @@
         <v>1180</v>
       </c>
       <c r="E25">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -5582,10 +5598,10 @@
         <v>1181</v>
       </c>
       <c r="E26">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -5599,10 +5615,10 @@
         <v>1182</v>
       </c>
       <c r="E27">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -5616,10 +5632,10 @@
         <v>1183</v>
       </c>
       <c r="E28">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -5633,10 +5649,10 @@
         <v>1184</v>
       </c>
       <c r="E29">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -5650,10 +5666,10 @@
         <v>1185</v>
       </c>
       <c r="E30">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -5667,10 +5683,10 @@
         <v>1186</v>
       </c>
       <c r="E31">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -5684,10 +5700,10 @@
         <v>1187</v>
       </c>
       <c r="E32">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -5701,10 +5717,10 @@
         <v>1188</v>
       </c>
       <c r="E33">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -5718,10 +5734,10 @@
         <v>1189</v>
       </c>
       <c r="E34">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -5735,10 +5751,10 @@
         <v>1190</v>
       </c>
       <c r="E35">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -5752,10 +5768,10 @@
         <v>1191</v>
       </c>
       <c r="E36">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -5769,10 +5785,10 @@
         <v>1192</v>
       </c>
       <c r="E37">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -5786,10 +5802,10 @@
         <v>1193</v>
       </c>
       <c r="E38">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -5803,10 +5819,10 @@
         <v>1194</v>
       </c>
       <c r="E39">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -5820,10 +5836,10 @@
         <v>1195</v>
       </c>
       <c r="E40">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -5837,10 +5853,10 @@
         <v>1196</v>
       </c>
       <c r="E41">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -5854,10 +5870,10 @@
         <v>1197</v>
       </c>
       <c r="E42">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -5871,10 +5887,10 @@
         <v>1198</v>
       </c>
       <c r="E43">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -5888,10 +5904,10 @@
         <v>1199</v>
       </c>
       <c r="E44">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -5905,10 +5921,10 @@
         <v>1200</v>
       </c>
       <c r="E45">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -5922,10 +5938,10 @@
         <v>1201</v>
       </c>
       <c r="E46">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -5939,10 +5955,10 @@
         <v>1202</v>
       </c>
       <c r="E47">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -5956,10 +5972,10 @@
         <v>1203</v>
       </c>
       <c r="E48">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -5973,10 +5989,10 @@
         <v>1204</v>
       </c>
       <c r="E49">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -5990,10 +6006,10 @@
         <v>1205</v>
       </c>
       <c r="E50">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -6007,10 +6023,10 @@
         <v>1206</v>
       </c>
       <c r="E51">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -6024,10 +6040,10 @@
         <v>1207</v>
       </c>
       <c r="E52">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -6041,10 +6057,10 @@
         <v>1208</v>
       </c>
       <c r="E53">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -6058,10 +6074,10 @@
         <v>1209</v>
       </c>
       <c r="E54">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -6075,10 +6091,10 @@
         <v>1210</v>
       </c>
       <c r="E55">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -6092,10 +6108,10 @@
         <v>1211</v>
       </c>
       <c r="E56">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -6109,10 +6125,10 @@
         <v>1212</v>
       </c>
       <c r="E57">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -6126,10 +6142,10 @@
         <v>1213</v>
       </c>
       <c r="E58">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -6143,10 +6159,10 @@
         <v>1214</v>
       </c>
       <c r="E59">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -6160,10 +6176,10 @@
         <v>1215</v>
       </c>
       <c r="E60">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -6177,10 +6193,10 @@
         <v>1216</v>
       </c>
       <c r="E61">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -6194,10 +6210,10 @@
         <v>1217</v>
       </c>
       <c r="E62">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -6211,10 +6227,10 @@
         <v>1218</v>
       </c>
       <c r="E63">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -6228,10 +6244,10 @@
         <v>1219</v>
       </c>
       <c r="E64">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -6245,10 +6261,10 @@
         <v>1220</v>
       </c>
       <c r="E65">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -6262,10 +6278,10 @@
         <v>1221</v>
       </c>
       <c r="E66">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -6279,10 +6295,10 @@
         <v>1222</v>
       </c>
       <c r="E67">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -6296,10 +6312,10 @@
         <v>1223</v>
       </c>
       <c r="E68">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -6313,10 +6329,10 @@
         <v>1224</v>
       </c>
       <c r="E69">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -6330,10 +6346,10 @@
         <v>1225</v>
       </c>
       <c r="E70">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -6347,10 +6363,10 @@
         <v>1226</v>
       </c>
       <c r="E71">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -6364,10 +6380,10 @@
         <v>1227</v>
       </c>
       <c r="E72">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -6381,10 +6397,10 @@
         <v>1228</v>
       </c>
       <c r="E73">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -6398,10 +6414,10 @@
         <v>1229</v>
       </c>
       <c r="E74">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -6415,10 +6431,10 @@
         <v>1230</v>
       </c>
       <c r="E75">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -6432,10 +6448,10 @@
         <v>1231</v>
       </c>
       <c r="E76">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -6449,10 +6465,10 @@
         <v>1232</v>
       </c>
       <c r="E77">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -6466,10 +6482,10 @@
         <v>1233</v>
       </c>
       <c r="E78">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -6483,10 +6499,10 @@
         <v>1234</v>
       </c>
       <c r="E79">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -6500,10 +6516,10 @@
         <v>1235</v>
       </c>
       <c r="E80">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -6517,10 +6533,10 @@
         <v>1236</v>
       </c>
       <c r="E81">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -6534,10 +6550,10 @@
         <v>1237</v>
       </c>
       <c r="E82">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -6551,10 +6567,10 @@
         <v>1238</v>
       </c>
       <c r="E83">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -6568,10 +6584,10 @@
         <v>1239</v>
       </c>
       <c r="E84">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -6585,10 +6601,10 @@
         <v>1240</v>
       </c>
       <c r="E85">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -6602,10 +6618,10 @@
         <v>1241</v>
       </c>
       <c r="E86">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -6619,10 +6635,10 @@
         <v>1242</v>
       </c>
       <c r="E87">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -6636,10 +6652,10 @@
         <v>1243</v>
       </c>
       <c r="E88">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -6653,10 +6669,10 @@
         <v>1244</v>
       </c>
       <c r="E89">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -6670,10 +6686,10 @@
         <v>1245</v>
       </c>
       <c r="E90">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -6687,10 +6703,10 @@
         <v>1246</v>
       </c>
       <c r="E91">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -6704,10 +6720,10 @@
         <v>1247</v>
       </c>
       <c r="E92">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -6721,10 +6737,10 @@
         <v>1248</v>
       </c>
       <c r="E93">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -6738,10 +6754,10 @@
         <v>1249</v>
       </c>
       <c r="E94">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -6755,10 +6771,10 @@
         <v>1250</v>
       </c>
       <c r="E95">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -6772,10 +6788,10 @@
         <v>1251</v>
       </c>
       <c r="E96">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -6789,10 +6805,10 @@
         <v>1252</v>
       </c>
       <c r="E97">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -6806,10 +6822,10 @@
         <v>1253</v>
       </c>
       <c r="E98">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -6823,10 +6839,10 @@
         <v>1254</v>
       </c>
       <c r="E99">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -6840,10 +6856,10 @@
         <v>1255</v>
       </c>
       <c r="E100">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>104</v>
       </c>
@@ -6857,10 +6873,10 @@
         <v>1256</v>
       </c>
       <c r="E101">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>105</v>
       </c>
@@ -6874,10 +6890,10 @@
         <v>1257</v>
       </c>
       <c r="E102">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>106</v>
       </c>
@@ -6891,10 +6907,10 @@
         <v>1258</v>
       </c>
       <c r="E103">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -6908,10 +6924,10 @@
         <v>1259</v>
       </c>
       <c r="E104">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>108</v>
       </c>
@@ -6925,10 +6941,10 @@
         <v>1260</v>
       </c>
       <c r="E105">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>109</v>
       </c>
@@ -6942,10 +6958,10 @@
         <v>1261</v>
       </c>
       <c r="E106">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>110</v>
       </c>
@@ -6959,10 +6975,10 @@
         <v>1262</v>
       </c>
       <c r="E107">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -6976,10 +6992,10 @@
         <v>1263</v>
       </c>
       <c r="E108">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>112</v>
       </c>
@@ -6993,10 +7009,10 @@
         <v>1264</v>
       </c>
       <c r="E109">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>113</v>
       </c>
@@ -7010,10 +7026,10 @@
         <v>1265</v>
       </c>
       <c r="E110">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>114</v>
       </c>
@@ -7027,10 +7043,10 @@
         <v>1266</v>
       </c>
       <c r="E111">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -7044,10 +7060,10 @@
         <v>1267</v>
       </c>
       <c r="E112">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>116</v>
       </c>
@@ -7061,10 +7077,10 @@
         <v>1268</v>
       </c>
       <c r="E113">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>117</v>
       </c>
@@ -7078,10 +7094,10 @@
         <v>1269</v>
       </c>
       <c r="E114">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>118</v>
       </c>
@@ -7095,10 +7111,10 @@
         <v>1270</v>
       </c>
       <c r="E115">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>119</v>
       </c>
@@ -7112,10 +7128,10 @@
         <v>1271</v>
       </c>
       <c r="E116">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -7129,10 +7145,10 @@
         <v>1272</v>
       </c>
       <c r="E117">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -7146,10 +7162,10 @@
         <v>1273</v>
       </c>
       <c r="E118">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>122</v>
       </c>
@@ -7163,10 +7179,10 @@
         <v>1274</v>
       </c>
       <c r="E119">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>123</v>
       </c>
@@ -7180,10 +7196,10 @@
         <v>1275</v>
       </c>
       <c r="E120">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>124</v>
       </c>
@@ -7197,10 +7213,10 @@
         <v>1276</v>
       </c>
       <c r="E121">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>125</v>
       </c>
@@ -7214,10 +7230,10 @@
         <v>1277</v>
       </c>
       <c r="E122">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>126</v>
       </c>
@@ -7231,10 +7247,10 @@
         <v>1278</v>
       </c>
       <c r="E123">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -7248,10 +7264,10 @@
         <v>1279</v>
       </c>
       <c r="E124">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>128</v>
       </c>
@@ -7265,10 +7281,10 @@
         <v>1280</v>
       </c>
       <c r="E125">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>129</v>
       </c>
@@ -7282,10 +7298,10 @@
         <v>1281</v>
       </c>
       <c r="E126">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>130</v>
       </c>
@@ -7299,10 +7315,10 @@
         <v>1282</v>
       </c>
       <c r="E127">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>131</v>
       </c>
@@ -7316,10 +7332,10 @@
         <v>1283</v>
       </c>
       <c r="E128">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>132</v>
       </c>
@@ -7333,10 +7349,10 @@
         <v>1284</v>
       </c>
       <c r="E129">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>133</v>
       </c>
@@ -7350,10 +7366,10 @@
         <v>1285</v>
       </c>
       <c r="E130">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -7367,10 +7383,10 @@
         <v>1286</v>
       </c>
       <c r="E131">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>135</v>
       </c>
@@ -7384,10 +7400,10 @@
         <v>1287</v>
       </c>
       <c r="E132">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>136</v>
       </c>
@@ -7401,10 +7417,10 @@
         <v>1288</v>
       </c>
       <c r="E133">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>137</v>
       </c>
@@ -7418,10 +7434,10 @@
         <v>1289</v>
       </c>
       <c r="E134">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -7435,10 +7451,10 @@
         <v>1290</v>
       </c>
       <c r="E135">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -7452,10 +7468,10 @@
         <v>1291</v>
       </c>
       <c r="E136">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -7469,10 +7485,10 @@
         <v>1292</v>
       </c>
       <c r="E137">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>141</v>
       </c>
@@ -7486,10 +7502,10 @@
         <v>1293</v>
       </c>
       <c r="E138">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>142</v>
       </c>
@@ -7503,10 +7519,10 @@
         <v>1294</v>
       </c>
       <c r="E139">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -7520,10 +7536,10 @@
         <v>1295</v>
       </c>
       <c r="E140">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>144</v>
       </c>
@@ -7537,10 +7553,10 @@
         <v>1296</v>
       </c>
       <c r="E141">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -7554,10 +7570,10 @@
         <v>1297</v>
       </c>
       <c r="E142">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -7571,10 +7587,10 @@
         <v>1298</v>
       </c>
       <c r="E143">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -7588,10 +7604,10 @@
         <v>1299</v>
       </c>
       <c r="E144">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>148</v>
       </c>
@@ -7605,10 +7621,10 @@
         <v>1300</v>
       </c>
       <c r="E145">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>149</v>
       </c>
@@ -7622,10 +7638,10 @@
         <v>1301</v>
       </c>
       <c r="E146">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -7639,10 +7655,10 @@
         <v>1302</v>
       </c>
       <c r="E147">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -7656,10 +7672,10 @@
         <v>1303</v>
       </c>
       <c r="E148">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>152</v>
       </c>
@@ -7673,10 +7689,10 @@
         <v>1304</v>
       </c>
       <c r="E149">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>153</v>
       </c>
@@ -7690,10 +7706,10 @@
         <v>1305</v>
       </c>
       <c r="E150">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -7707,10 +7723,10 @@
         <v>1306</v>
       </c>
       <c r="E151">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>155</v>
       </c>
@@ -7724,10 +7740,10 @@
         <v>1307</v>
       </c>
       <c r="E152">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>156</v>
       </c>
@@ -7741,10 +7757,10 @@
         <v>1308</v>
       </c>
       <c r="E153">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>157</v>
       </c>
@@ -7758,10 +7774,10 @@
         <v>1309</v>
       </c>
       <c r="E154">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>158</v>
       </c>
@@ -7775,10 +7791,10 @@
         <v>1310</v>
       </c>
       <c r="E155">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>159</v>
       </c>
@@ -7792,10 +7808,10 @@
         <v>1311</v>
       </c>
       <c r="E156">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -7809,10 +7825,10 @@
         <v>1312</v>
       </c>
       <c r="E157">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>161</v>
       </c>
@@ -7826,10 +7842,10 @@
         <v>1313</v>
       </c>
       <c r="E158">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -7843,10 +7859,10 @@
         <v>1314</v>
       </c>
       <c r="E159">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>163</v>
       </c>
@@ -7860,10 +7876,10 @@
         <v>1315</v>
       </c>
       <c r="E160">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>164</v>
       </c>
@@ -7877,10 +7893,10 @@
         <v>1316</v>
       </c>
       <c r="E161">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>165</v>
       </c>
@@ -7894,10 +7910,10 @@
         <v>1317</v>
       </c>
       <c r="E162">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -7911,10 +7927,10 @@
         <v>1318</v>
       </c>
       <c r="E163">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>167</v>
       </c>
@@ -7928,10 +7944,10 @@
         <v>1319</v>
       </c>
       <c r="E164">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -7945,10 +7961,10 @@
         <v>1320</v>
       </c>
       <c r="E165">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>169</v>
       </c>
@@ -7962,10 +7978,10 @@
         <v>1321</v>
       </c>
       <c r="E166">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -7979,10 +7995,10 @@
         <v>1322</v>
       </c>
       <c r="E167">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>171</v>
       </c>
@@ -7996,10 +8012,10 @@
         <v>1323</v>
       </c>
       <c r="E168">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -8013,10 +8029,10 @@
         <v>1324</v>
       </c>
       <c r="E169">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>173</v>
       </c>
@@ -8030,10 +8046,10 @@
         <v>1325</v>
       </c>
       <c r="E170">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>174</v>
       </c>
@@ -8047,10 +8063,10 @@
         <v>1326</v>
       </c>
       <c r="E171">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>175</v>
       </c>
@@ -8064,10 +8080,10 @@
         <v>1327</v>
       </c>
       <c r="E172">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>176</v>
       </c>
@@ -8081,10 +8097,10 @@
         <v>1328</v>
       </c>
       <c r="E173">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>177</v>
       </c>
@@ -8098,10 +8114,10 @@
         <v>1329</v>
       </c>
       <c r="E174">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>178</v>
       </c>
@@ -8115,10 +8131,10 @@
         <v>1330</v>
       </c>
       <c r="E175">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>179</v>
       </c>
@@ -8132,10 +8148,10 @@
         <v>1331</v>
       </c>
       <c r="E176">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>180</v>
       </c>
@@ -8149,10 +8165,10 @@
         <v>1332</v>
       </c>
       <c r="E177">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>181</v>
       </c>
@@ -8166,10 +8182,10 @@
         <v>1333</v>
       </c>
       <c r="E178">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>182</v>
       </c>
@@ -8183,10 +8199,10 @@
         <v>1334</v>
       </c>
       <c r="E179">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>183</v>
       </c>
@@ -8200,10 +8216,10 @@
         <v>1335</v>
       </c>
       <c r="E180">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>184</v>
       </c>
@@ -8217,10 +8233,10 @@
         <v>1336</v>
       </c>
       <c r="E181">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>185</v>
       </c>
@@ -8234,10 +8250,10 @@
         <v>1337</v>
       </c>
       <c r="E182">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>186</v>
       </c>
@@ -8251,10 +8267,10 @@
         <v>1338</v>
       </c>
       <c r="E183">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>187</v>
       </c>
@@ -8268,10 +8284,10 @@
         <v>1339</v>
       </c>
       <c r="E184">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -8285,10 +8301,10 @@
         <v>1340</v>
       </c>
       <c r="E185">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>189</v>
       </c>
@@ -8302,10 +8318,10 @@
         <v>1341</v>
       </c>
       <c r="E186">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>190</v>
       </c>
@@ -8319,10 +8335,10 @@
         <v>1342</v>
       </c>
       <c r="E187">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>191</v>
       </c>
@@ -8336,10 +8352,10 @@
         <v>1343</v>
       </c>
       <c r="E188">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>192</v>
       </c>
@@ -8353,10 +8369,10 @@
         <v>1344</v>
       </c>
       <c r="E189">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>193</v>
       </c>
@@ -8370,10 +8386,10 @@
         <v>1345</v>
       </c>
       <c r="E190">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>194</v>
       </c>
@@ -8387,10 +8403,10 @@
         <v>1346</v>
       </c>
       <c r="E191">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>195</v>
       </c>
@@ -8404,10 +8420,10 @@
         <v>1347</v>
       </c>
       <c r="E192">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>196</v>
       </c>
@@ -8421,10 +8437,10 @@
         <v>1348</v>
       </c>
       <c r="E193">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>197</v>
       </c>
@@ -8438,10 +8454,10 @@
         <v>1349</v>
       </c>
       <c r="E194">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>198</v>
       </c>
@@ -8455,10 +8471,10 @@
         <v>1350</v>
       </c>
       <c r="E195">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -8472,10 +8488,10 @@
         <v>1351</v>
       </c>
       <c r="E196">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>200</v>
       </c>
@@ -8489,10 +8505,10 @@
         <v>1352</v>
       </c>
       <c r="E197">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>201</v>
       </c>
@@ -8506,10 +8522,10 @@
         <v>1353</v>
       </c>
       <c r="E198">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>202</v>
       </c>
@@ -8523,10 +8539,10 @@
         <v>1354</v>
       </c>
       <c r="E199">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>203</v>
       </c>
@@ -8540,10 +8556,10 @@
         <v>1355</v>
       </c>
       <c r="E200">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>204</v>
       </c>
@@ -8557,10 +8573,10 @@
         <v>1356</v>
       </c>
       <c r="E201">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -8574,10 +8590,10 @@
         <v>1357</v>
       </c>
       <c r="E202">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>206</v>
       </c>
@@ -8591,10 +8607,10 @@
         <v>1358</v>
       </c>
       <c r="E203">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>207</v>
       </c>
@@ -8608,10 +8624,10 @@
         <v>1359</v>
       </c>
       <c r="E204">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>208</v>
       </c>
@@ -8625,10 +8641,10 @@
         <v>1360</v>
       </c>
       <c r="E205">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>209</v>
       </c>
@@ -8642,10 +8658,10 @@
         <v>1361</v>
       </c>
       <c r="E206">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>210</v>
       </c>
@@ -8659,10 +8675,10 @@
         <v>1362</v>
       </c>
       <c r="E207">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>211</v>
       </c>
@@ -8676,10 +8692,10 @@
         <v>1363</v>
       </c>
       <c r="E208">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>212</v>
       </c>
@@ -8693,10 +8709,10 @@
         <v>1364</v>
       </c>
       <c r="E209">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>213</v>
       </c>
@@ -8710,10 +8726,10 @@
         <v>1365</v>
       </c>
       <c r="E210">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>214</v>
       </c>
@@ -8727,10 +8743,10 @@
         <v>1366</v>
       </c>
       <c r="E211">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>215</v>
       </c>
@@ -8744,10 +8760,10 @@
         <v>1367</v>
       </c>
       <c r="E212">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>216</v>
       </c>
@@ -8761,10 +8777,10 @@
         <v>1368</v>
       </c>
       <c r="E213">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>217</v>
       </c>
@@ -8778,10 +8794,10 @@
         <v>1369</v>
       </c>
       <c r="E214">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>218</v>
       </c>
@@ -8795,10 +8811,10 @@
         <v>1370</v>
       </c>
       <c r="E215">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>219</v>
       </c>
@@ -8812,10 +8828,10 @@
         <v>1371</v>
       </c>
       <c r="E216">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>220</v>
       </c>
@@ -8829,10 +8845,10 @@
         <v>1372</v>
       </c>
       <c r="E217">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>221</v>
       </c>
@@ -8846,10 +8862,10 @@
         <v>1373</v>
       </c>
       <c r="E218">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -8863,10 +8879,10 @@
         <v>1374</v>
       </c>
       <c r="E219">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>223</v>
       </c>
@@ -8880,10 +8896,10 @@
         <v>1375</v>
       </c>
       <c r="E220">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>224</v>
       </c>
@@ -8897,10 +8913,10 @@
         <v>1376</v>
       </c>
       <c r="E221">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>225</v>
       </c>
@@ -8914,10 +8930,10 @@
         <v>1377</v>
       </c>
       <c r="E222">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>226</v>
       </c>
@@ -8931,10 +8947,10 @@
         <v>1378</v>
       </c>
       <c r="E223">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>227</v>
       </c>
@@ -8948,10 +8964,10 @@
         <v>1379</v>
       </c>
       <c r="E224">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>228</v>
       </c>
@@ -8965,10 +8981,10 @@
         <v>1380</v>
       </c>
       <c r="E225">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>229</v>
       </c>
@@ -8982,10 +8998,10 @@
         <v>1381</v>
       </c>
       <c r="E226">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>230</v>
       </c>
@@ -8999,10 +9015,10 @@
         <v>1382</v>
       </c>
       <c r="E227">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>231</v>
       </c>
@@ -9016,10 +9032,10 @@
         <v>1383</v>
       </c>
       <c r="E228">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>232</v>
       </c>
@@ -9033,10 +9049,10 @@
         <v>1384</v>
       </c>
       <c r="E229">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>233</v>
       </c>
@@ -9050,10 +9066,10 @@
         <v>1385</v>
       </c>
       <c r="E230">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>234</v>
       </c>
@@ -9067,10 +9083,10 @@
         <v>1386</v>
       </c>
       <c r="E231">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>235</v>
       </c>
@@ -9084,10 +9100,10 @@
         <v>1387</v>
       </c>
       <c r="E232">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>236</v>
       </c>
@@ -9101,10 +9117,10 @@
         <v>1388</v>
       </c>
       <c r="E233">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>237</v>
       </c>
@@ -9118,10 +9134,10 @@
         <v>1389</v>
       </c>
       <c r="E234">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>238</v>
       </c>
@@ -9135,10 +9151,10 @@
         <v>1390</v>
       </c>
       <c r="E235">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>239</v>
       </c>
@@ -9152,10 +9168,10 @@
         <v>1391</v>
       </c>
       <c r="E236">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>240</v>
       </c>
@@ -9169,10 +9185,10 @@
         <v>1392</v>
       </c>
       <c r="E237">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>241</v>
       </c>
@@ -9186,10 +9202,10 @@
         <v>1393</v>
       </c>
       <c r="E238">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>242</v>
       </c>
@@ -9203,10 +9219,10 @@
         <v>1394</v>
       </c>
       <c r="E239">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>243</v>
       </c>
@@ -9220,10 +9236,10 @@
         <v>1395</v>
       </c>
       <c r="E240">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>244</v>
       </c>
@@ -9237,10 +9253,10 @@
         <v>1396</v>
       </c>
       <c r="E241">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>245</v>
       </c>
@@ -9254,10 +9270,10 @@
         <v>1397</v>
       </c>
       <c r="E242">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>246</v>
       </c>
@@ -9271,10 +9287,10 @@
         <v>1398</v>
       </c>
       <c r="E243">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>247</v>
       </c>
@@ -9288,10 +9304,10 @@
         <v>1399</v>
       </c>
       <c r="E244">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>248</v>
       </c>
@@ -9305,10 +9321,10 @@
         <v>1400</v>
       </c>
       <c r="E245">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>249</v>
       </c>
@@ -9322,10 +9338,10 @@
         <v>1401</v>
       </c>
       <c r="E246">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>250</v>
       </c>
@@ -9339,10 +9355,10 @@
         <v>1402</v>
       </c>
       <c r="E247">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>251</v>
       </c>
@@ -9356,10 +9372,10 @@
         <v>1403</v>
       </c>
       <c r="E248">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>252</v>
       </c>
@@ -9373,10 +9389,10 @@
         <v>1404</v>
       </c>
       <c r="E249">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>253</v>
       </c>
@@ -9390,10 +9406,10 @@
         <v>1405</v>
       </c>
       <c r="E250">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>254</v>
       </c>
@@ -9407,10 +9423,10 @@
         <v>1406</v>
       </c>
       <c r="E251">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>255</v>
       </c>
@@ -9424,10 +9440,10 @@
         <v>1407</v>
       </c>
       <c r="E252">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>256</v>
       </c>
@@ -9441,10 +9457,10 @@
         <v>1408</v>
       </c>
       <c r="E253">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -9458,10 +9474,10 @@
         <v>1409</v>
       </c>
       <c r="E254">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -9475,10 +9491,10 @@
         <v>1410</v>
       </c>
       <c r="E255">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>259</v>
       </c>
@@ -9492,10 +9508,10 @@
         <v>1411</v>
       </c>
       <c r="E256">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -9509,10 +9525,10 @@
         <v>1412</v>
       </c>
       <c r="E257">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>261</v>
       </c>
@@ -9526,10 +9542,10 @@
         <v>1413</v>
       </c>
       <c r="E258">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>262</v>
       </c>
@@ -9543,10 +9559,10 @@
         <v>1414</v>
       </c>
       <c r="E259">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>263</v>
       </c>
@@ -9560,10 +9576,10 @@
         <v>1415</v>
       </c>
       <c r="E260">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>264</v>
       </c>
@@ -9577,10 +9593,10 @@
         <v>1416</v>
       </c>
       <c r="E261">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>265</v>
       </c>
@@ -9594,10 +9610,10 @@
         <v>1417</v>
       </c>
       <c r="E262">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -9611,10 +9627,10 @@
         <v>1418</v>
       </c>
       <c r="E263">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>267</v>
       </c>
@@ -9628,10 +9644,10 @@
         <v>1419</v>
       </c>
       <c r="E264">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>268</v>
       </c>
@@ -9645,10 +9661,10 @@
         <v>1420</v>
       </c>
       <c r="E265">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -9662,10 +9678,10 @@
         <v>1421</v>
       </c>
       <c r="E266">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>270</v>
       </c>
@@ -9679,10 +9695,10 @@
         <v>1422</v>
       </c>
       <c r="E267">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>271</v>
       </c>
@@ -9696,10 +9712,10 @@
         <v>1423</v>
       </c>
       <c r="E268">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>272</v>
       </c>
@@ -9713,10 +9729,10 @@
         <v>1424</v>
       </c>
       <c r="E269">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>273</v>
       </c>
@@ -9730,10 +9746,10 @@
         <v>1425</v>
       </c>
       <c r="E270">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>274</v>
       </c>
@@ -9747,10 +9763,10 @@
         <v>1426</v>
       </c>
       <c r="E271">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>275</v>
       </c>
@@ -9764,10 +9780,10 @@
         <v>1427</v>
       </c>
       <c r="E272">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>276</v>
       </c>
@@ -9781,10 +9797,10 @@
         <v>1428</v>
       </c>
       <c r="E273">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>277</v>
       </c>
@@ -9798,10 +9814,10 @@
         <v>1429</v>
       </c>
       <c r="E274">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>278</v>
       </c>
@@ -9815,10 +9831,10 @@
         <v>1430</v>
       </c>
       <c r="E275">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>279</v>
       </c>
@@ -9832,10 +9848,10 @@
         <v>1431</v>
       </c>
       <c r="E276">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>280</v>
       </c>
@@ -9849,10 +9865,10 @@
         <v>1432</v>
       </c>
       <c r="E277">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>281</v>
       </c>
@@ -9866,10 +9882,10 @@
         <v>1433</v>
       </c>
       <c r="E278">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>282</v>
       </c>
@@ -9883,10 +9899,10 @@
         <v>1434</v>
       </c>
       <c r="E279">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>283</v>
       </c>
@@ -9900,10 +9916,10 @@
         <v>1435</v>
       </c>
       <c r="E280">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>284</v>
       </c>
@@ -9917,10 +9933,10 @@
         <v>1436</v>
       </c>
       <c r="E281">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>285</v>
       </c>
@@ -9934,10 +9950,10 @@
         <v>1437</v>
       </c>
       <c r="E282">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>286</v>
       </c>
@@ -9951,10 +9967,10 @@
         <v>1438</v>
       </c>
       <c r="E283">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>287</v>
       </c>
@@ -9968,10 +9984,10 @@
         <v>1439</v>
       </c>
       <c r="E284">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>288</v>
       </c>
@@ -9985,10 +10001,10 @@
         <v>1440</v>
       </c>
       <c r="E285">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>289</v>
       </c>
@@ -10002,10 +10018,10 @@
         <v>1441</v>
       </c>
       <c r="E286">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>290</v>
       </c>
@@ -10019,10 +10035,10 @@
         <v>1442</v>
       </c>
       <c r="E287">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>291</v>
       </c>
@@ -10036,10 +10052,10 @@
         <v>1443</v>
       </c>
       <c r="E288">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>292</v>
       </c>
@@ -10053,10 +10069,10 @@
         <v>1444</v>
       </c>
       <c r="E289">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>293</v>
       </c>
@@ -10070,10 +10086,10 @@
         <v>1445</v>
       </c>
       <c r="E290">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>294</v>
       </c>
@@ -10087,10 +10103,10 @@
         <v>1446</v>
       </c>
       <c r="E291">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>295</v>
       </c>
@@ -10104,10 +10120,10 @@
         <v>1447</v>
       </c>
       <c r="E292">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>296</v>
       </c>
@@ -10121,10 +10137,10 @@
         <v>1448</v>
       </c>
       <c r="E293">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>297</v>
       </c>
@@ -10138,10 +10154,10 @@
         <v>1449</v>
       </c>
       <c r="E294">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>298</v>
       </c>
@@ -10155,10 +10171,10 @@
         <v>1450</v>
       </c>
       <c r="E295">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>299</v>
       </c>
@@ -10172,10 +10188,10 @@
         <v>1451</v>
       </c>
       <c r="E296">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>300</v>
       </c>
@@ -10189,10 +10205,10 @@
         <v>1452</v>
       </c>
       <c r="E297">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>301</v>
       </c>
@@ -10206,10 +10222,10 @@
         <v>1453</v>
       </c>
       <c r="E298">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>302</v>
       </c>
@@ -10223,10 +10239,10 @@
         <v>1454</v>
       </c>
       <c r="E299">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>303</v>
       </c>
@@ -10240,10 +10256,10 @@
         <v>1455</v>
       </c>
       <c r="E300">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>304</v>
       </c>
@@ -10257,10 +10273,10 @@
         <v>1456</v>
       </c>
       <c r="E301">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>305</v>
       </c>
@@ -10274,10 +10290,10 @@
         <v>1457</v>
       </c>
       <c r="E302">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>306</v>
       </c>
@@ -10291,10 +10307,10 @@
         <v>1458</v>
       </c>
       <c r="E303">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>307</v>
       </c>
@@ -10308,10 +10324,10 @@
         <v>1459</v>
       </c>
       <c r="E304">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>308</v>
       </c>
@@ -10325,10 +10341,10 @@
         <v>1460</v>
       </c>
       <c r="E305">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>309</v>
       </c>
@@ -10342,10 +10358,10 @@
         <v>1461</v>
       </c>
       <c r="E306">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>310</v>
       </c>
@@ -10359,10 +10375,10 @@
         <v>1462</v>
       </c>
       <c r="E307">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>311</v>
       </c>
@@ -10376,10 +10392,10 @@
         <v>1463</v>
       </c>
       <c r="E308">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>312</v>
       </c>
@@ -10393,10 +10409,10 @@
         <v>1464</v>
       </c>
       <c r="E309">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>313</v>
       </c>
@@ -10410,10 +10426,10 @@
         <v>1465</v>
       </c>
       <c r="E310">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>314</v>
       </c>
@@ -10427,10 +10443,10 @@
         <v>1466</v>
       </c>
       <c r="E311">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>315</v>
       </c>
@@ -10444,10 +10460,10 @@
         <v>1467</v>
       </c>
       <c r="E312">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>316</v>
       </c>
@@ -10461,10 +10477,10 @@
         <v>1468</v>
       </c>
       <c r="E313">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>317</v>
       </c>
@@ -10478,10 +10494,10 @@
         <v>1469</v>
       </c>
       <c r="E314">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>318</v>
       </c>
@@ -10495,10 +10511,10 @@
         <v>1470</v>
       </c>
       <c r="E315">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>319</v>
       </c>
@@ -10512,10 +10528,10 @@
         <v>1471</v>
       </c>
       <c r="E316">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>320</v>
       </c>
@@ -10529,10 +10545,10 @@
         <v>1472</v>
       </c>
       <c r="E317">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>321</v>
       </c>
@@ -10546,10 +10562,10 @@
         <v>1473</v>
       </c>
       <c r="E318">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>322</v>
       </c>
@@ -10563,10 +10579,10 @@
         <v>1474</v>
       </c>
       <c r="E319">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>323</v>
       </c>
@@ -10580,10 +10596,10 @@
         <v>1475</v>
       </c>
       <c r="E320">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>324</v>
       </c>
@@ -10597,10 +10613,10 @@
         <v>1476</v>
       </c>
       <c r="E321">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>325</v>
       </c>
@@ -10614,10 +10630,10 @@
         <v>1477</v>
       </c>
       <c r="E322">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>326</v>
       </c>
@@ -10631,10 +10647,10 @@
         <v>1478</v>
       </c>
       <c r="E323">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>327</v>
       </c>
@@ -10648,10 +10664,10 @@
         <v>1479</v>
       </c>
       <c r="E324">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>328</v>
       </c>
@@ -10665,10 +10681,10 @@
         <v>1480</v>
       </c>
       <c r="E325">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>329</v>
       </c>
@@ -10682,10 +10698,10 @@
         <v>1481</v>
       </c>
       <c r="E326">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>330</v>
       </c>
@@ -10699,10 +10715,10 @@
         <v>1482</v>
       </c>
       <c r="E327">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>331</v>
       </c>
@@ -10716,10 +10732,10 @@
         <v>1483</v>
       </c>
       <c r="E328">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>332</v>
       </c>
@@ -10733,10 +10749,10 @@
         <v>1484</v>
       </c>
       <c r="E329">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>333</v>
       </c>
@@ -10750,10 +10766,10 @@
         <v>1485</v>
       </c>
       <c r="E330">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>334</v>
       </c>
@@ -10767,10 +10783,10 @@
         <v>1486</v>
       </c>
       <c r="E331">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>335</v>
       </c>
@@ -10784,10 +10800,10 @@
         <v>1487</v>
       </c>
       <c r="E332">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>336</v>
       </c>
@@ -10801,10 +10817,10 @@
         <v>1488</v>
       </c>
       <c r="E333">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>337</v>
       </c>
@@ -10818,10 +10834,10 @@
         <v>1489</v>
       </c>
       <c r="E334">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>338</v>
       </c>
@@ -10835,10 +10851,10 @@
         <v>1490</v>
       </c>
       <c r="E335">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>339</v>
       </c>
@@ -10852,10 +10868,10 @@
         <v>1491</v>
       </c>
       <c r="E336">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>340</v>
       </c>
@@ -10869,10 +10885,10 @@
         <v>1492</v>
       </c>
       <c r="E337">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>341</v>
       </c>
@@ -10886,10 +10902,10 @@
         <v>1493</v>
       </c>
       <c r="E338">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>342</v>
       </c>
@@ -10903,10 +10919,10 @@
         <v>1494</v>
       </c>
       <c r="E339">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>343</v>
       </c>
@@ -10920,10 +10936,10 @@
         <v>1495</v>
       </c>
       <c r="E340">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>344</v>
       </c>
@@ -10937,10 +10953,10 @@
         <v>1496</v>
       </c>
       <c r="E341">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>345</v>
       </c>
@@ -10954,10 +10970,10 @@
         <v>1497</v>
       </c>
       <c r="E342">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>346</v>
       </c>
@@ -10971,10 +10987,10 @@
         <v>1498</v>
       </c>
       <c r="E343">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>347</v>
       </c>
@@ -10988,10 +11004,10 @@
         <v>1499</v>
       </c>
       <c r="E344">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>348</v>
       </c>
@@ -11005,10 +11021,10 @@
         <v>1500</v>
       </c>
       <c r="E345">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>349</v>
       </c>
@@ -11022,10 +11038,10 @@
         <v>1501</v>
       </c>
       <c r="E346">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>350</v>
       </c>
@@ -11039,10 +11055,10 @@
         <v>1502</v>
       </c>
       <c r="E347">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>351</v>
       </c>
@@ -11056,10 +11072,10 @@
         <v>1503</v>
       </c>
       <c r="E348">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>352</v>
       </c>
@@ -11073,10 +11089,10 @@
         <v>1504</v>
       </c>
       <c r="E349">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>353</v>
       </c>
@@ -11090,10 +11106,10 @@
         <v>1505</v>
       </c>
       <c r="E350">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>354</v>
       </c>
@@ -11107,10 +11123,10 @@
         <v>1506</v>
       </c>
       <c r="E351">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>355</v>
       </c>
@@ -11124,10 +11140,10 @@
         <v>1507</v>
       </c>
       <c r="E352">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>356</v>
       </c>
@@ -11141,10 +11157,10 @@
         <v>1508</v>
       </c>
       <c r="E353">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>357</v>
       </c>
@@ -11158,10 +11174,10 @@
         <v>1509</v>
       </c>
       <c r="E354">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>358</v>
       </c>
@@ -11175,10 +11191,10 @@
         <v>1510</v>
       </c>
       <c r="E355">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>359</v>
       </c>
@@ -11192,10 +11208,10 @@
         <v>1511</v>
       </c>
       <c r="E356">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>360</v>
       </c>
@@ -11209,10 +11225,10 @@
         <v>1512</v>
       </c>
       <c r="E357">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>361</v>
       </c>
@@ -11226,10 +11242,10 @@
         <v>1513</v>
       </c>
       <c r="E358">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>362</v>
       </c>
@@ -11243,10 +11259,10 @@
         <v>1514</v>
       </c>
       <c r="E359">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>363</v>
       </c>
@@ -11260,10 +11276,10 @@
         <v>1515</v>
       </c>
       <c r="E360">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>364</v>
       </c>
@@ -11277,10 +11293,10 @@
         <v>1516</v>
       </c>
       <c r="E361">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>365</v>
       </c>
@@ -11294,10 +11310,10 @@
         <v>1517</v>
       </c>
       <c r="E362">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>366</v>
       </c>
@@ -11311,10 +11327,10 @@
         <v>1518</v>
       </c>
       <c r="E363">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>367</v>
       </c>
@@ -11328,10 +11344,10 @@
         <v>1519</v>
       </c>
       <c r="E364">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>368</v>
       </c>
@@ -11345,10 +11361,10 @@
         <v>1520</v>
       </c>
       <c r="E365">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>369</v>
       </c>
@@ -11362,10 +11378,10 @@
         <v>1521</v>
       </c>
       <c r="E366">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>370</v>
       </c>
@@ -11379,10 +11395,10 @@
         <v>1522</v>
       </c>
       <c r="E367">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>371</v>
       </c>
@@ -11396,10 +11412,10 @@
         <v>1523</v>
       </c>
       <c r="E368">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>372</v>
       </c>
@@ -11413,10 +11429,10 @@
         <v>1524</v>
       </c>
       <c r="E369">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>373</v>
       </c>
@@ -11430,10 +11446,10 @@
         <v>1525</v>
       </c>
       <c r="E370">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>374</v>
       </c>
@@ -11447,10 +11463,10 @@
         <v>1526</v>
       </c>
       <c r="E371">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>375</v>
       </c>
@@ -11464,10 +11480,10 @@
         <v>1527</v>
       </c>
       <c r="E372">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>376</v>
       </c>
@@ -11481,10 +11497,10 @@
         <v>1528</v>
       </c>
       <c r="E373">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>377</v>
       </c>
@@ -11498,10 +11514,10 @@
         <v>1529</v>
       </c>
       <c r="E374">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>378</v>
       </c>
@@ -11515,10 +11531,10 @@
         <v>1530</v>
       </c>
       <c r="E375">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>379</v>
       </c>
@@ -11532,10 +11548,10 @@
         <v>1531</v>
       </c>
       <c r="E376">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>380</v>
       </c>
@@ -11549,10 +11565,10 @@
         <v>1532</v>
       </c>
       <c r="E377">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>381</v>
       </c>
@@ -11566,10 +11582,10 @@
         <v>1533</v>
       </c>
       <c r="E378">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>382</v>
       </c>
@@ -11583,10 +11599,10 @@
         <v>1534</v>
       </c>
       <c r="E379">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>383</v>
       </c>
@@ -11600,10 +11616,10 @@
         <v>1535</v>
       </c>
       <c r="E380">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>384</v>
       </c>
@@ -11617,10 +11633,10 @@
         <v>1536</v>
       </c>
       <c r="E381">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>385</v>
       </c>
@@ -11634,10 +11650,10 @@
         <v>1537</v>
       </c>
       <c r="E382">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>386</v>
       </c>
@@ -11651,10 +11667,10 @@
         <v>1538</v>
       </c>
       <c r="E383">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>387</v>
       </c>
@@ -11668,10 +11684,10 @@
         <v>1539</v>
       </c>
       <c r="E384">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>388</v>
       </c>
@@ -11685,7 +11701,7 @@
         <v>1540</v>
       </c>
       <c r="E385">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -11694,14 +11710,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="24" width="38.7109375" customWidth="1"/>
+    <col min="1" max="24" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1565</v>
       </c>
@@ -11778,7 +11794,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1">
+    <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1566</v>
       </c>
@@ -11855,7 +11871,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1567</v>
       </c>
@@ -11932,7 +11948,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="2" customFormat="1">
+    <row r="4" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1568</v>
       </c>
@@ -12009,7 +12025,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1569</v>
       </c>
@@ -12086,7 +12102,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="6" spans="1:25" s="2" customFormat="1">
+    <row r="6" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1570</v>
       </c>
@@ -12163,7 +12179,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1571</v>
       </c>
@@ -12240,7 +12256,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="2" customFormat="1">
+    <row r="8" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1572</v>
       </c>
@@ -12317,7 +12333,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1573</v>
       </c>
@@ -12394,7 +12410,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:25" s="2" customFormat="1">
+    <row r="10" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1574</v>
       </c>
@@ -12471,7 +12487,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1575</v>
       </c>
@@ -12548,7 +12564,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1">
+    <row r="12" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1576</v>
       </c>
@@ -12625,7 +12641,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1577</v>
       </c>
@@ -12702,7 +12718,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="2" customFormat="1">
+    <row r="14" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1578</v>
       </c>
@@ -12779,7 +12795,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1579</v>
       </c>
@@ -12856,7 +12872,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="2" customFormat="1">
+    <row r="16" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1580</v>
       </c>
@@ -12933,7 +12949,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>1581</v>
       </c>
@@ -13016,15 +13032,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="3.7109375" customWidth="1"/>
-    <col min="10" max="24" width="4.7109375" customWidth="1"/>
+    <col min="1" max="9" width="3.6640625" customWidth="1"/>
+    <col min="10" max="24" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1565</v>
       </c>
@@ -13101,7 +13117,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1566</v>
       </c>
@@ -13178,7 +13194,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1567</v>
       </c>
@@ -13255,7 +13271,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1568</v>
       </c>
@@ -13332,7 +13348,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1569</v>
       </c>
@@ -13409,7 +13425,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1570</v>
       </c>
@@ -13486,7 +13502,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1571</v>
       </c>
@@ -13563,7 +13579,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1572</v>
       </c>
@@ -13640,7 +13656,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1573</v>
       </c>
@@ -13717,7 +13733,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1574</v>
       </c>
@@ -13794,7 +13810,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1575</v>
       </c>
@@ -13871,7 +13887,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1576</v>
       </c>
@@ -13948,7 +13964,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1577</v>
       </c>
@@ -14025,7 +14041,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1578</v>
       </c>
@@ -14102,7 +14118,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1579</v>
       </c>
@@ -14179,7 +14195,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1580</v>
       </c>
@@ -14256,7 +14272,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>1581</v>
       </c>
